--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_37_R4.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_37_R4.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0046</v>
+        <v>10.5093</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3346</v>
+        <v>8.570499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>1.9388</v>
       </c>
       <c r="G2" t="n">
         <v>4.6991</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4498</v>
+        <v>0.0549</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1142</v>
+        <v>0.3501</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5641</v>
+        <v>-0.2952</v>
       </c>
       <c r="V2" t="n">
         <v>5.7553</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.2445</v>
+        <v>10.2435</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4947</v>
+        <v>8.426399999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7498</v>
+        <v>1.817</v>
       </c>
       <c r="G3" t="n">
         <v>6.5965</v>
@@ -688,13 +688,13 @@
         <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1896</v>
+        <v>-0.1907</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8883</v>
+        <v>0.0435</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3014</v>
+        <v>-0.2341</v>
       </c>
       <c r="V3" t="n">
         <v>1.7501</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3598</v>
+        <v>3.5309</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8051</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5547</v>
+        <v>2.8489</v>
       </c>
       <c r="G4" t="n">
         <v>1.6121</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2116</v>
+        <v>1.3827</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1102</v>
+        <v>0.9871</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1013</v>
+        <v>0.3956</v>
       </c>
       <c r="V4" t="n">
         <v>0.5361</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9752</v>
+        <v>3.4924</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2337</v>
+        <v>2.2463</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7415</v>
+        <v>1.2461</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3473</v>
+        <v>3.4718</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6037</v>
+        <v>-0.2556</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9511</v>
+        <v>3.7274</v>
       </c>
       <c r="J5" t="n">
-        <v>3.173</v>
+        <v>2.1674</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5175</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6904</v>
+        <v>1.5289</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8256</v>
+        <v>1.3043</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0862</v>
+        <v>-0.8942</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7393999999999999</v>
+        <v>2.1985</v>
       </c>
       <c r="P5" t="n">
         <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.6237</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7834</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5403</v>
+        <v>-0.067</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6844</v>
+        <v>0.0788</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1441</v>
+        <v>-0.1458</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5323</v>
+        <v>2.7947</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4206</v>
+        <v>1.986</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1116</v>
+        <v>0.8087</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4718</v>
+        <v>2.3473</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2556</v>
+        <v>-0.6037</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7274</v>
+        <v>2.9511</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1674</v>
+        <v>3.173</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6385999999999999</v>
+        <v>-0.5175</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5289</v>
+        <v>3.6904</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3043</v>
+        <v>-0.8256</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8942</v>
+        <v>-0.0862</v>
       </c>
       <c r="O6" t="n">
-        <v>2.1985</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P6" t="n">
         <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>2.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0271</v>
+        <v>0.3598</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7468</v>
+        <v>0.4367</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2803</v>
+        <v>-0.0769</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1824</v>
+        <v>1.7893</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0504</v>
+        <v>-0.3427</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2328</v>
+        <v>2.1319</v>
       </c>
       <c r="G7" t="n">
         <v>2.6061</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.496</v>
+        <v>0.1109</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4402</v>
+        <v>0.2675</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0558</v>
+        <v>-0.1566</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0036</v>
+        <v>0.5472</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4437</v>
+        <v>-0.1017</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4473</v>
+        <v>0.649</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0052</v>
@@ -1078,13 +1078,13 @@
         <v>2.5515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4551</v>
+        <v>0.0885</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0272</v>
+        <v>0.3148</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4279</v>
+        <v>-0.2262</v>
       </c>
       <c r="V8" t="n">
         <v>0.5361</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2107</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4618</v>
+        <v>-1.0201</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2511</v>
+        <v>0.3855</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3552</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.825</v>
+        <v>0.4011</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0578</v>
+        <v>0.4995</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2328</v>
+        <v>-0.0984</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. BAKO</t>
+          <t>J. AYAYI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.157</v>
+        <v>-2.1438</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3521</v>
+        <v>-0.2809</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5091</v>
+        <v>-1.863</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5575</v>
+        <v>-0.7441</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4537</v>
+        <v>0.012</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1038</v>
+        <v>-0.7562</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.2459</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.3697</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.1239</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2323</v>
+        <v>-0.99</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3361</v>
+        <v>-0.3577</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1038</v>
+        <v>-0.6323</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2702</v>
+        <v>-0.0413</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5623</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2921</v>
+        <v>0.0215</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.2166</v>
+        <v>-2.2862</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.2166</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. AYAYI</t>
+          <t>I. BAKO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3872</v>
+        <v>-2.2846</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5915</v>
+        <v>1.1909</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7957</v>
+        <v>-3.4755</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7441</v>
+        <v>0.5575</v>
       </c>
       <c r="H11" t="n">
-        <v>0.012</v>
+        <v>0.4537</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7562</v>
+        <v>0.1038</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2459</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3697</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1239</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.99</v>
+        <v>-0.2323</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3577</v>
+        <v>-0.3361</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6323</v>
+        <v>0.1038</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2847</v>
+        <v>0.1426</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3734</v>
+        <v>0.4011</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0887</v>
+        <v>-0.2585</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.2862</v>
+        <v>-3.2166</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.2862</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8709</v>
+        <v>-3.4342</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0105</v>
+        <v>-1.2714</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8604</v>
+        <v>-2.1628</v>
       </c>
       <c r="G12" t="n">
         <v>0.3445</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1586</v>
+        <v>0.2781</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7468</v>
+        <v>-0.0077</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.2858</v>
       </c>
       <c r="V12" t="n">
         <v>-4.2888</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.375</v>
+        <v>-4.8702</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.7285</v>
+        <v>-6.4926</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3536</v>
+        <v>1.6224</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7423</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2926</v>
+        <v>0.2122</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1142</v>
+        <v>0.3501</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4068</v>
+        <v>-0.1379</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7886</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.3016</v>
+        <v>19.5399</v>
       </c>
       <c r="E14" t="n">
-        <v>12.3544</v>
+        <v>13.5927</v>
       </c>
       <c r="F14" t="n">
-        <v>5.947199999999999</v>
+        <v>5.946999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>17.3881</v>
       </c>
       <c r="H14" t="n">
-        <v>5.041499999999999</v>
+        <v>5.0415</v>
       </c>
       <c r="I14" t="n">
         <v>12.3468</v>
@@ -1528,7 +1528,7 @@
         <v>5.8372</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8211000000000008</v>
+        <v>0.8210999999999999</v>
       </c>
       <c r="N14" t="n">
         <v>-5.688400000000001</v>
@@ -1537,7 +1537,7 @@
         <v>6.509399999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>4.639200000000001</v>
+        <v>4.6392</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.9173</v>
@@ -1546,13 +1546,13 @@
         <v>18.5563</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4936</v>
+        <v>2.7318</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4204</v>
+        <v>3.6587</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9271000000000003</v>
+        <v>-0.9267</v>
       </c>
       <c r="V14" t="n">
         <v>-5.2192</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.646</v>
+        <v>3.9604</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4572</v>
+        <v>2.5135</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1888</v>
+        <v>1.4469</v>
       </c>
       <c r="G15" t="n">
         <v>1.8721</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8615</v>
+        <v>0.1759</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2898</v>
+        <v>0.3462</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4283</v>
+        <v>-0.1702</v>
       </c>
       <c r="V15" t="n">
         <v>2.1444</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4435</v>
+        <v>2.4949</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8203</v>
+        <v>3.1741</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3768</v>
+        <v>-0.6793</v>
       </c>
       <c r="G16" t="n">
         <v>-2.6173</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4573</v>
+        <v>-0.4059</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7978</v>
+        <v>-0.4439</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3405</v>
+        <v>0.038</v>
       </c>
       <c r="V16" t="n">
         <v>3.8945</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2733</v>
+        <v>-0.3969</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0447</v>
+        <v>-0.1326</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7714</v>
+        <v>-0.2643</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0467</v>
+        <v>-0.4155</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6481</v>
+        <v>-0.1512</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3986</v>
+        <v>-0.2643</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3277</v>
+        <v>0.0168</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0672</v>
+        <v>0.0168</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3949</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.719</v>
+        <v>-0.4323</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7153</v>
+        <v>-0.168</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0037</v>
+        <v>-0.2643</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6241</v>
+        <v>0.0187</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3724</v>
+        <v>-0.1494</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2517</v>
+        <v>0.168</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4977</v>
+        <v>-0.6304</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1326</v>
+        <v>0.219</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3651</v>
+        <v>-0.8494</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4155</v>
+        <v>-2.0467</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1512</v>
+        <v>-0.6481</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2643</v>
+        <v>-1.3986</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0168</v>
+        <v>-0.3277</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0168</v>
+        <v>0.0672</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.3949</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4323</v>
+        <v>-1.719</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.168</v>
+        <v>-0.7153</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2643</v>
+        <v>-1.0037</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.7205</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1494</v>
+        <v>0.5467</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0672</v>
+        <v>0.1737</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8182</v>
+        <v>-0.6331</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0332</v>
+        <v>0.0848</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7851</v>
+        <v>-0.7178</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0307</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1792</v>
+        <v>0.0059</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0668</v>
+        <v>0.0512</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7503</v>
+        <v>-1.0809</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1936</v>
+        <v>1.6931</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9439</v>
+        <v>-2.774</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.289</v>
+        <v>-1.3983</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6446</v>
+        <v>-0.9398</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9336</v>
+        <v>-0.4585</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6096</v>
+        <v>2.1509</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2217</v>
+        <v>0.6589</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3879</v>
+        <v>1.492</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8986</v>
+        <v>-3.5492</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5771</v>
+        <v>-1.5987</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3215</v>
+        <v>-1.9505</v>
       </c>
       <c r="P20" t="n">
         <v>-0.232</v>
@@ -2014,28 +2014,28 @@
         <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0154</v>
+        <v>-0.7754</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1687</v>
+        <v>-0.2827</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1533</v>
+        <v>-0.4927</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.214</v>
+        <v>1.3247</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2862</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0403</v>
+        <v>-1.5137</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1034</v>
+        <v>1.6654</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1437</v>
+        <v>-3.1791</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3983</v>
+        <v>-0.289</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9398</v>
+        <v>0.6446</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4585</v>
+        <v>-0.9336</v>
       </c>
       <c r="J21" t="n">
-        <v>2.1509</v>
+        <v>2.6096</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6589</v>
+        <v>2.2217</v>
       </c>
       <c r="L21" t="n">
-        <v>1.492</v>
+        <v>0.3879</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.5492</v>
+        <v>-2.8986</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5987</v>
+        <v>-1.5771</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9505</v>
+        <v>-1.3215</v>
       </c>
       <c r="P21" t="n">
         <v>-0.232</v>
@@ -2092,28 +2092,28 @@
         <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7348</v>
+        <v>0.2212</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8725000000000001</v>
+        <v>0.3031</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8623</v>
+        <v>-0.0819</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3247</v>
+        <v>-1.214</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8197</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1569</v>
+        <v>-3.1086</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4337</v>
+        <v>-2.1757</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7231</v>
+        <v>-0.9329</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0089</v>
+        <v>-1.5564</v>
       </c>
       <c r="H22" t="n">
-        <v>0.287</v>
+        <v>-1.1751</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.2959</v>
+        <v>-0.3814</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8892</v>
+        <v>-0.2694</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7176</v>
+        <v>0.3697</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6067</v>
+        <v>-0.6391</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1198</v>
+        <v>-1.287</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4306</v>
+        <v>-1.5448</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6891</v>
+        <v>0.2578</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4577</v>
+        <v>-0.0187</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7749</v>
+        <v>0.2715</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3172</v>
+        <v>-0.2902</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.165</v>
+        <v>-3.5614</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1757</v>
+        <v>-2.9055</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.6559</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5564</v>
+        <v>-3.0089</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1751</v>
+        <v>0.287</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3814</v>
+        <v>-3.2959</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2694</v>
+        <v>-0.8892</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3697</v>
+        <v>1.7176</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6391</v>
+        <v>-2.6067</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.287</v>
+        <v>-2.1198</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5448</v>
+        <v>-1.4306</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2578</v>
+        <v>-0.6891</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0751</v>
+        <v>0.0532</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2715</v>
+        <v>0.3031</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3466</v>
+        <v>-0.25</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1418</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5288</v>
+        <v>-4.0012</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6546</v>
+        <v>-2.4187</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8742</v>
+        <v>-1.5826</v>
       </c>
       <c r="G24" t="n">
         <v>-0.928</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.673</v>
+        <v>-0.1454</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2829</v>
+        <v>-0.047</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3901</v>
+        <v>-0.0984</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7316</v>
+        <v>-4.3391</v>
       </c>
       <c r="E25" t="n">
         <v>-3.6711</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0605</v>
+        <v>-0.668</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1283</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4589</v>
+        <v>-1.0664</v>
       </c>
       <c r="T25" t="n">
         <v>-0.4323</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0266</v>
+        <v>-0.6341</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.9754</v>
+        <v>-4.7052</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.4654</v>
+        <v>-3.9936</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.51</v>
+        <v>-0.7116</v>
       </c>
       <c r="G26" t="n">
         <v>-3.841</v>
@@ -2482,13 +2482,13 @@
         <v>1.8556</v>
       </c>
       <c r="S26" t="n">
-        <v>0.239</v>
+        <v>0.5091</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0114</v>
+        <v>0.4604</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2504</v>
+        <v>0.0488</v>
       </c>
       <c r="V26" t="n">
         <v>2.5697</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.3014</v>
+        <v>-17.5152</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.947100000000001</v>
+        <v>-5.9473</v>
       </c>
       <c r="F27" t="n">
-        <v>-12.3544</v>
+        <v>-11.568</v>
       </c>
       <c r="G27" t="n">
         <v>-17.388</v>
@@ -2533,7 +2533,7 @@
         <v>-12.3468</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8211000000000004</v>
+        <v>-0.8210999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>5.688199999999999</v>
@@ -2560,13 +2560,13 @@
         <v>13.9172</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.4935</v>
+        <v>-0.7072999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>0.9268000000000005</v>
+        <v>0.9268999999999998</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.4205</v>
+        <v>-1.6342</v>
       </c>
       <c r="V27" t="n">
         <v>5.2191</v>
